--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -459,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -477,7 +477,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -603,7 +603,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -639,7 +639,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Column List</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -657,7 +657,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Categorization Values Currently in Use</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -895,7 +895,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Data Dictionary</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -913,7 +913,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -931,7 +931,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -949,7 +949,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
+          <t>Dot Py Parameter Reference List</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -967,20 +967,56 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Dot Py Parameter Reference List</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dot Py Parameter Reference List</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Process Values Currently in Use</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dot Py Parameter Reference List</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>File Manipulation/ Management</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -459,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -477,7 +477,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Python String Documentation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -495,7 +495,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Excel File Creation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -513,7 +513,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Manual File Creator</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -549,25 +549,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -577,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -585,7 +589,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -595,7 +599,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -603,7 +607,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -621,7 +625,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -631,7 +635,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -639,7 +643,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -649,7 +653,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -657,7 +661,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -667,7 +671,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -675,29 +679,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -715,7 +715,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -733,7 +733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -751,7 +751,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -769,7 +769,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -787,7 +787,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -805,7 +805,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -823,7 +823,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Dot Py Categorization Reference List</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -841,17 +841,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Statistics</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -877,7 +877,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Categorization Values Currently in Use</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -895,128 +895,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Process Values Currently in Use</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>File Manipulation/ Management</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -459,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Algorithm Taxonomy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -477,7 +477,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Python String Documentation</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -495,7 +495,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -513,7 +513,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -549,24 +549,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -599,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -617,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -635,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -653,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -671,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -689,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -707,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -725,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -743,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dot Py String Classification</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -761,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -779,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -797,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Data Dictionary Columns</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -815,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -828,15 +824,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -900,17 +900,731 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Filter Order</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Theorem</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Clustering</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Density Estimation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dimensionality Reduction</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Feature Transformation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Generative Models</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Graph Algorithms</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Information Retrieval</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ranking / Recommendation</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Time Series Forecasting</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OS Folder Management</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Directory Management</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Excel File Creation</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>
       </c>
     </row>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -824,19 +824,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -846,15 +842,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Theorem</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Theorem</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1098,37 +1098,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Density Estimation</t>
+          <t>Clustering</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction</t>
+          <t>Density Estimation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Dimensionality Reduction</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Feature Transformation</t>
+          <t>Feature Selection (AC)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Generative Models</t>
+          <t>Feature Transformation</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Generative Models</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prediction</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ranking / Recommendation</t>
+          <t>Prediction</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Ranking / Recommendation</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Time Series Forecasting</t>
+          <t>Reinforcement Learning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1408,37 +1408,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
-        </is>
-      </c>
+          <t>Time Series Forecasting</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OS Folder Management</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>OS Folder Management</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1502,37 +1502,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Directory Management</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>File Management</t>
+          <t>Directory Management</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>File Management</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Excel File Creation</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1614,15 +1614,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Data Engineering</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Documentation Taxonomy Categorization</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dot Py String Classification</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>ML Definitions</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -842,19 +842,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>ML Model</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -869,7 +865,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>ML Training</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -887,7 +883,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -905,7 +901,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -923,7 +919,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -941,7 +937,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -959,7 +955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Neural Network</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -977,7 +973,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -995,7 +991,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1013,7 +1009,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1031,7 +1027,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Vector Database</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1049,7 +1045,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Vector Search</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1062,15 +1058,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Theorem</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1116,24 +1116,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1143,7 +1139,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1151,7 +1147,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1161,7 +1157,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1169,7 +1165,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1179,7 +1175,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1187,7 +1183,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1197,7 +1193,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Density Estimation</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1205,7 +1201,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1215,7 +1211,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1223,7 +1219,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1233,7 +1229,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Feature Selection (AC)</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1241,7 +1237,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1251,7 +1247,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Feature Transformation</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1259,7 +1255,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1269,7 +1265,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Generative Models</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1277,7 +1273,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1295,7 +1291,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1305,7 +1301,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1313,7 +1309,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1331,7 +1327,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1341,7 +1337,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prediction</t>
+          <t>Theorem</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1349,7 +1345,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1359,7 +1355,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ranking / Recommendation</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1367,7 +1363,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1377,7 +1373,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1385,20 +1381,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Time Series Forecasting</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1426,24 +1426,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
-        </is>
-      </c>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1453,7 +1449,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OS Folder Management</t>
+          <t>Clustering</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1461,7 +1457,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1471,7 +1467,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Density Estimation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1479,7 +1475,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1489,7 +1485,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Dimensionality Reduction</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1497,7 +1493,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1507,7 +1503,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Feature Selection (AC)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1515,29 +1511,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Feature Transformation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1547,7 +1539,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Directory Management</t>
+          <t>Generative Models</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1555,7 +1547,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1565,7 +1557,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>File Management</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1573,7 +1565,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1583,7 +1575,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1591,7 +1583,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1601,7 +1593,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1609,7 +1601,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1619,7 +1611,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Prediction</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1627,20 +1619,298 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ranking / Recommendation</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Time Series Forecasting</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OS Folder Management</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Directory Management</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Excel File Creation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Manual File Creator</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -541,7 +541,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Data Dictionary Columns</t>
+          <t>Clustering</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Data Engineering</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Documentation Taxonomy Categorization</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dot Py String Classification</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ML Definitions</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ML Model</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ML Training</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>ML Definitions</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>ML Model</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>ML Training</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Neural Network</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vector Database</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vector Search</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1058,19 +1058,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1085,7 +1081,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Neural Network</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1103,7 +1099,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Organization Taxonomy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1139,7 +1135,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1157,7 +1153,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Development</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1193,7 +1189,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1211,7 +1207,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Validation/ Model Selection</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1229,7 +1225,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Vector Database</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1247,7 +1243,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Vector Search</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1260,15 +1256,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Theorem</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1386,24 +1386,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1413,7 +1409,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1421,7 +1417,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1431,7 +1427,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1439,7 +1435,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1449,7 +1445,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1457,7 +1453,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1467,7 +1463,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Density Estimation</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1475,7 +1471,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1485,7 +1481,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1493,7 +1489,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1503,7 +1499,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Feature Selection (AC)</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1511,7 +1507,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1521,7 +1517,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Feature Transformation</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1529,7 +1525,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1539,7 +1535,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Generative Models</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1547,7 +1543,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1557,7 +1553,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1565,7 +1561,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1575,7 +1571,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Theorem</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1583,7 +1579,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1593,7 +1589,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1601,7 +1597,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1611,7 +1607,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prediction</t>
+          <t xml:space="preserve">Trade-offs </t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1619,7 +1615,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1629,7 +1625,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ranking / Recommendation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1637,20 +1633,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Time Series Forecasting</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1696,24 +1696,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
-        </is>
-      </c>
+          <t>Clustering</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1723,7 +1719,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OS Folder Management</t>
+          <t>Density Estimation</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1731,7 +1727,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1741,7 +1737,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Dimensionality Reduction</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1749,7 +1745,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1759,7 +1755,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Feature Selection (AC)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1767,7 +1763,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1777,7 +1773,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Feature Transformation</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1785,29 +1781,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Generative Models</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1817,7 +1809,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Directory Management</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1825,7 +1817,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1835,7 +1827,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>File Management</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1843,7 +1835,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1853,7 +1845,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -1861,7 +1853,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1871,7 +1863,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Prediction</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1879,7 +1871,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Algorithm Categorization</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1889,7 +1881,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Ranking / Recommendation</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1897,20 +1889,280 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Time Series Forecasting</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OS Folder Management</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Directory Management</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Excel File Creation</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Cardinal Presentation Sins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Clustering</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Data Dictionary Columns</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Data Engineering</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Documentation Taxonomy Categorization</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dot Py String Classification</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ML Definitions</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ML Model</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ML Training</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>ML Definitions</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>ML Model</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>ML Training</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Neural Network</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Organization Taxonomy</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Process Development</t>
+          <t>Neural Network</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Notes from Books</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Organization Taxonomy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Validation/ Model Selection</t>
+          <t>Persuasion</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vector Database</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vector Search</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1256,19 +1256,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1283,7 +1279,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Process Development</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1301,7 +1297,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1319,7 +1315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Consideration</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1337,7 +1333,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Story Telling Tenants</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1355,7 +1351,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Supervised Learning</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1373,7 +1369,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1391,7 +1387,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Types of Problems</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1409,7 +1405,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1427,7 +1423,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1445,7 +1441,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Understand Your Visuals</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1463,7 +1459,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Validation/ Model Selection</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1481,7 +1477,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Vector Database</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1499,7 +1495,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Vector Search</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1512,15 +1508,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Theorem</t>
+          <t>Cardinal Presentation Sins</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trade-offs </t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1638,24 +1638,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1673,7 +1669,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1691,7 +1687,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1701,7 +1697,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1709,7 +1705,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1719,7 +1715,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Density Estimation</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1727,7 +1723,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1737,7 +1733,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1745,7 +1741,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1755,7 +1751,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Feature Selection (AC)</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1763,7 +1759,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1773,7 +1769,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Feature Transformation</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1781,7 +1777,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1791,7 +1787,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Generative Models</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1799,7 +1795,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1809,7 +1805,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1817,7 +1813,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1827,7 +1823,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1835,7 +1831,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1845,7 +1841,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -1853,7 +1849,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1863,7 +1859,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prediction</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1871,7 +1867,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1881,7 +1877,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ranking / Recommendation</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1889,7 +1885,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1899,7 +1895,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -1907,7 +1903,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1917,7 +1913,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -1925,7 +1921,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1935,7 +1931,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Time Series Forecasting</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -1943,29 +1939,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1975,7 +1967,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OS Folder Management</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -1983,7 +1975,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1993,7 +1985,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2001,7 +1993,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2011,7 +2003,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2019,7 +2011,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2029,7 +2021,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2037,29 +2029,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2069,7 +2057,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Directory Management</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -2077,7 +2065,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2087,7 +2075,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>File Management</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2095,7 +2083,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2105,7 +2093,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2113,7 +2101,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2123,7 +2111,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Story Telling</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2131,7 +2119,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2141,7 +2129,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Storytelling</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2149,20 +2137,716 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Technology Adoption</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Theorem</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Validation/ Model Selection</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Clustering</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Density Estimation</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dimensionality Reduction</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Feature Selection (AC)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Feature Transformation</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Generative Models</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Graph Algorithms</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Information Retrieval</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ranking / Recommendation</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Representation Learning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Time Series Forecasting</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Algorithm Categorization</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>OS Folder Management</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Directory Management</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Excel File Creation</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algorithm Taxonomy</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Clustering</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Data Dictionary Columns</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Data Engineering</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Documentation Taxonomy Categorization</t>
+          <t>Density Estimation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dot Py String Classification</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Dimensionality Reduction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Feature Transformation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Function</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ML Definitions</t>
+          <t>Generative Models</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ML Model</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ML Training</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Hadoop</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Make it as Short as Possible</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Learning Paradigm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>ML Definitions</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>ML Model Taxonomy</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>ML Training</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neural Network</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Notes from Books</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Organization Taxonomy</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Persuasion</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Presentation Tenants</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Process Development</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Neural Network</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Story Telling Tenants</t>
+          <t>Notes from Books</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Supervised Learning</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Organization Taxonomy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Types of Problems</t>
+          <t>Persuasion</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Validation/ Model Selection</t>
+          <t>Process Development</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vector Database</t>
+          <t>Ranking / Recommendation</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vector Search</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1508,19 +1508,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1535,7 +1531,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Reinforcement Learning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1553,7 +1549,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Representation Learning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1571,7 +1567,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cardinal Presentation Sins</t>
+          <t>Similarity</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1589,7 +1585,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1607,7 +1603,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Consideration</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1625,7 +1621,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Story Telling Tenants</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1643,7 +1639,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Supervised Learning</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -1661,7 +1657,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Time Series Forecasting</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1697,7 +1693,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1715,7 +1711,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>Types of Problems</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1733,7 +1729,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1751,7 +1747,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1769,7 +1765,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Understand Your Visuals</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1787,7 +1783,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Validation/ Model Selection</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1805,7 +1801,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Vector Database</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1823,7 +1819,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Vector Search</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1836,15 +1832,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Make it as Short as Possible</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Cardinal Presentation Sins</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Story Telling</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Storytelling</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Technology Adoption</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Theorem</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Validation/ Model Selection</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -2304,24 +2304,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2331,7 +2327,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Anomaly Detection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -2339,7 +2335,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2349,7 +2345,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -2357,7 +2353,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2367,7 +2363,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -2375,7 +2371,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2385,7 +2381,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Density Estimation</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -2393,7 +2389,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2403,7 +2399,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -2411,7 +2407,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2421,7 +2417,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Feature Selection (AC)</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -2429,7 +2425,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2439,7 +2435,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Feature Transformation</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -2447,7 +2443,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2457,7 +2453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Generative Models</t>
+          <t>Story Telling</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -2465,7 +2461,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2475,7 +2471,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>Storytelling</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -2483,7 +2479,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2493,7 +2489,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Technology Adoption</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -2501,7 +2497,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2511,7 +2507,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Theorem</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -2519,7 +2515,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2529,7 +2525,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prediction</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -2537,7 +2533,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2547,7 +2543,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ranking / Recommendation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -2555,7 +2551,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2565,7 +2561,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -2573,7 +2569,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2583,7 +2579,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -2591,7 +2587,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2601,7 +2597,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Representation Learning</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -2609,7 +2605,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2619,7 +2615,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Time Series Forecasting</t>
+          <t>Understand Your Visuals</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -2627,42 +2623,42 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Algorithm Categorization, used to Categorize ML Methods in Algorithm Taxonomy</t>
-        </is>
-      </c>
+          <t>Validation/ Model Selection</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OS Folder Management</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2677,7 +2673,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>OS Folder Management</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -2695,7 +2691,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -2726,37 +2722,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Directory Management</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2771,7 +2767,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>File Management</t>
+          <t>Directory Management</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -2789,7 +2785,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>File Management</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -2807,7 +2803,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Excel File Creation</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -2838,15 +2834,33 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>

--- a/Streamlit/Data/object_auto_published.xlsx
+++ b/Streamlit/Data/object_auto_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algorithm Categorization</t>
+          <t>Activation Function</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Categorization</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clustering</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Clustering</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Data Dictionary Columns</t>
+          <t>Confusion Matrix</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Data Engineering</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Density Estimation</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dimensionality Reduction</t>
+          <t>Density Estimation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Documentation Taxonomy Categorization</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dot Py String Classification</t>
+          <t>Dimensionality Reduction</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Dot Py String Classification</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Dot Py String Taxonomy Process</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Feature Transformation</t>
+          <t>Experiement Design</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Function</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Generative Models</t>
+          <t>Feature Transformation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Function</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Graph Algorithms</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hadoop</t>
+          <t>Generative Models</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Information Retrieval</t>
+          <t>Graph Algorithms</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Graph Theory</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Learning Paradigm</t>
+          <t>Hadoop</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ML Definitions</t>
+          <t>Hyperparameter</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ML Model Taxonomy</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ML Training</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Make it as Short as Possible</t>
+          <t>Learning Paradigm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>ML Definitions</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>ML Model Taxonomy</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>ML Training</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Neural Network</t>
+          <t>Method Approach</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Notes from Books</t>
+          <t>Method Objective</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Organization Taxonomy</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Persuasion</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Presentation Tenants</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Process Development</t>
+          <t>Neural Network</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ranking / Recommendation</t>
+          <t>Notes from Books</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Organization Taxonomy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Persuasion</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Representation Learning</t>
+          <t>Presentation Tenants</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Similarity</t>
+          <t>Principle</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Story Telling Tenants</t>
+          <t>Process Development</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Supervised Learning</t>
+          <t>Ranking / Recommendation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Time Series Forecasting</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tooling</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reinforcement Learning</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Types of Problems</t>
+          <t>Representation Learning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
+          <t>Similarity</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Validation/ Model Selection</t>
+          <t>Story Telling Tenants</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vector Database</t>
+          <t>Supervised Learning</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vector Search</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1832,19 +1832,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Time Series Forecasting</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1859,7 +1855,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1895,7 +1891,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cardinal Presentation Sins</t>
+          <t>Types of Problems</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -1913,7 +1909,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -1931,7 +1927,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Consideration</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -1949,7 +1945,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Understand Your Visuals</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -1967,7 +1963,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Validation/ Model Selection</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -1985,7 +1981,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Vector Database</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2003,7 +1999,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Vector Search</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2021,7 +2017,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>Wicked Problem</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2034,15 +2030,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Automating Python</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Cardinal Presentation Sins</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Consideration</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Make it as Short as Possible</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Defintion</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Make it as Short as Possible</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Story Telling</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Storytelling</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Technology Adoption</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Theorem</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Validation/ Model Selection</t>
+          <t>Re-enforce the Message</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -2646,24 +2646,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OS Folder Management</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -2681,7 +2677,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2691,7 +2687,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -2699,7 +2695,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2709,7 +2705,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -2717,7 +2713,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2727,7 +2723,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Story Telling</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -2735,29 +2731,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Process</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Storytelling</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2767,7 +2759,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Directory Management</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -2775,7 +2767,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2785,7 +2777,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>File Management</t>
+          <t>Technology Adoption</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -2793,7 +2785,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2803,7 +2795,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Excel File Creation</t>
+          <t>Theorem</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -2811,7 +2803,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2821,7 +2813,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -2829,7 +2821,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Dot Py String Taxonomy Categorization</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2839,7 +2831,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Manual File Creator</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -2847,20 +2839,316 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Validation/ Model Selection</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>OS Folder Management</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Process</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Directory Management</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Excel File Creation</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="D149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Dot Py String Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
         </is>
